--- a/qa-docs/test-cases/Done/Authentication/VerseByVerse_Signup_Test_Cases.xlsx
+++ b/qa-docs/test-cases/Done/Authentication/VerseByVerse_Signup_Test_Cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\versebyverse-quality-engineering\qa-docs\test-cases\Authentication\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\versebyverse-quality-engineering\qa-docs\test-cases\Done\Authentication\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCBA517-82F5-422F-BABD-C63841E66BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2D4516-A736-4816-AB4E-EB5CD05E3F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="135">
   <si>
     <t>VerseByVerse — Signup Test Cases</t>
   </si>
@@ -240,11 +240,6 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>1. Enter valid values for all required fields
-2. Enter a password longer than the maximum allowed length
-3. Submit the form</t>
-  </si>
-  <si>
     <t>AUTH-SIGNUP-011</t>
   </si>
   <si>
@@ -499,6 +494,32 @@
   <si>
     <t>The UI clearly communicates that verification is required or what the next action is
 The message is actionable and not ambiguous</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>**Fix
+Minor change:  Create Account button disabled</t>
+  </si>
+  <si>
+    <t>** Fix
+Create Account submission blocked for all subsequent missing form tests</t>
+  </si>
+  <si>
+    <t>Added a logic where password can not contain exact word matching username</t>
+  </si>
+  <si>
+    <t>1. Enter valid values for all required fields
+2. Enter a password longer than the maximum allowed length  (72 characters)
+3. Submit the form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max length: 72 char
+Fixed * browser was clipping characters past 72 char.  </t>
+  </si>
+  <si>
+    <t>Username only takes letters, numbers, dot, and underscore</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1027,9 @@
         <v>17</v>
       </c>
       <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
+      <c r="I3" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J3" s="6"/>
     </row>
     <row r="4" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -1032,8 +1055,12 @@
         <v>24</v>
       </c>
       <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="6"/>
+      <c r="I4" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -1058,8 +1085,12 @@
         <v>28</v>
       </c>
       <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
+      <c r="I5" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -1084,7 +1115,9 @@
         <v>32</v>
       </c>
       <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J6" s="6"/>
     </row>
     <row r="7" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -1110,7 +1143,9 @@
         <v>36</v>
       </c>
       <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J7" s="6"/>
     </row>
     <row r="8" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -1136,7 +1171,9 @@
         <v>41</v>
       </c>
       <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
+      <c r="I8" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J8" s="6"/>
     </row>
     <row r="9" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -1162,7 +1199,9 @@
         <v>46</v>
       </c>
       <c r="H9" s="4"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -1188,7 +1227,9 @@
         <v>50</v>
       </c>
       <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
+      <c r="I10" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J10" s="6"/>
     </row>
     <row r="11" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -1214,8 +1255,12 @@
         <v>54</v>
       </c>
       <c r="H11" s="4"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="6"/>
+      <c r="I11" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -1234,21 +1279,25 @@
         <v>22</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>50</v>
       </c>
       <c r="H12" s="4"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="6"/>
+      <c r="I12" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>20</v>
@@ -1260,21 +1309,25 @@
         <v>22</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="5"/>
+      <c r="H13" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>64</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>57</v>
@@ -1286,21 +1339,23 @@
         <v>22</v>
       </c>
       <c r="F14" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>66</v>
-      </c>
       <c r="H14" s="4"/>
-      <c r="I14" s="5"/>
+      <c r="I14" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J14" s="6"/>
     </row>
     <row r="15" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>57</v>
@@ -1312,21 +1367,23 @@
         <v>22</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H15" s="4"/>
-      <c r="I15" s="5"/>
+      <c r="I15" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J15" s="6"/>
     </row>
     <row r="16" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>57</v>
@@ -1338,21 +1395,23 @@
         <v>22</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H16" s="4"/>
-      <c r="I16" s="5"/>
+      <c r="I16" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J16" s="6"/>
     </row>
     <row r="17" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>57</v>
@@ -1364,21 +1423,23 @@
         <v>22</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H17" s="4"/>
-      <c r="I17" s="5"/>
+      <c r="I17" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>77</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>57</v>
@@ -1390,24 +1451,26 @@
         <v>22</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>79</v>
-      </c>
       <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
+      <c r="I18" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J18" s="6"/>
     </row>
     <row r="19" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>21</v>
@@ -1416,21 +1479,23 @@
         <v>22</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="H19" s="4"/>
-      <c r="I19" s="5"/>
+      <c r="I19" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J19" s="6"/>
     </row>
     <row r="20" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>86</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>57</v>
@@ -1442,21 +1507,23 @@
         <v>22</v>
       </c>
       <c r="F20" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>88</v>
-      </c>
       <c r="H20" s="4"/>
-      <c r="I20" s="5"/>
+      <c r="I20" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>20</v>
@@ -1468,21 +1535,23 @@
         <v>22</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="H21" s="4"/>
-      <c r="I21" s="5"/>
+      <c r="I21" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>94</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>20</v>
@@ -1494,177 +1563,191 @@
         <v>22</v>
       </c>
       <c r="F22" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>96</v>
-      </c>
       <c r="H22" s="4"/>
-      <c r="I22" s="5"/>
+      <c r="I22" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J22" s="6"/>
     </row>
     <row r="23" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="H23" s="4"/>
-      <c r="I23" s="5"/>
+      <c r="I23" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J23" s="6"/>
     </row>
     <row r="24" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>104</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="F24" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>106</v>
-      </c>
       <c r="H24" s="4"/>
-      <c r="I24" s="5"/>
+      <c r="I24" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J24" s="6"/>
     </row>
     <row r="25" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="H25" s="4"/>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H26" s="4"/>
-      <c r="I26" s="5"/>
+      <c r="I26" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J26" s="6"/>
     </row>
     <row r="27" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
+      <c r="I27" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J27" s="6"/>
     </row>
     <row r="28" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>120</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>121</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="G28" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>124</v>
-      </c>
       <c r="H28" s="4"/>
-      <c r="I28" s="5"/>
+      <c r="I28" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J28" s="6"/>
     </row>
     <row r="29" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>57</v>
@@ -1673,16 +1756,18 @@
         <v>21</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="H29" s="4"/>
-      <c r="I29" s="5"/>
+      <c r="I29" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="J29" s="6"/>
     </row>
   </sheetData>
